--- a/docs/案件DD/土地権利買取_上限価格試算_和歌山3案件.xlsx
+++ b/docs/案件DD/土地権利買取_上限価格試算_和歌山3案件.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -113,11 +113,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -488,15 +487,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,7 +508,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>考え方：完成品としてPXが支払える価格から、設備・工事・負担金・諸経費・PXの利益を引いた残りが「土地＋連系権利」に払える上限。黄色セルは前提値（変更すると再計算）。単位は万円。</t>
+          <t>考え方：完成品の販売価格から、機材・工事・負担金を引いた残りが「土地＋連系権利」に払える上限。PXの利益は機材価格（粗利約30%）に含む前提。黄色セルは前提値（変更すると再計算）。単位は万円。</t>
         </is>
       </c>
     </row>
@@ -549,21 +548,21 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>完成品（ターンキー）としての価値</t>
+          <t>完成品の販売価格（基本ケース）</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>65000</v>
+        <v>50000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>65000</v>
+        <v>50000</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>65000</v>
+        <v>50000</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>青建の希望価格6.5億円(税抜)。類似：JHD荘川蓄電所(2MW/8MWh)約7億円(2026/7)。PX社内の買取基準があればここを置換</t>
+          <t>現状の販売見込み5.0〜5.5億円。基本は下限の5.0億円で置く</t>
         </is>
       </c>
     </row>
@@ -575,21 +574,21 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>蓄電池＋PCS＋EPC（造成・基礎・電気工事）</t>
+          <t>機材（蓄電池・PCS・監視盤・受電設備・輸送・試験）</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>40000</v>
+        <v>38000</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>40000</v>
+        <v>38000</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>40000</v>
+        <v>38000</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Mega Power2507×3=7,521kWh。全体で約5.3万円/kWhと仮定（METI資料は2022〜24年度で6.0〜7.6万円/kWh、足元は低下傾向）</t>
+          <t>PX見積(MP2507×3, 2026/3)の税抜合計3.86億円＝基本3.8億円。粗利約30%込み（原価2.7億円）</t>
         </is>
       </c>
     </row>
@@ -601,21 +600,21 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>系統連系 工事費負担金（税込）</t>
+          <t>工事費（基礎・設置・電気・造成など）</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>637</v>
+        <v>5000</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1291</v>
+        <v>5000</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6375</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>関電送配電 回答書の確定値。協議で増額の可能性あり</t>
+          <t>通常約5,000万円</t>
         </is>
       </c>
     </row>
@@ -627,21 +626,21 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>許認可・設計・保険・金利等の諸経費</t>
+          <t>系統連系 工事費負担金（税込）</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3000</v>
+        <v>637</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3000</v>
+        <v>1291</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>3000</v>
+        <v>6375</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>開発許可・農地転用・消防・設計・建中金利などの概算</t>
+          <t>関電送配電 回答書の確定値。協議で増額の可能性あり</t>
         </is>
       </c>
     </row>
@@ -653,79 +652,79 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>PXの開発利益・リスク料（完成品価値に対する率）</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.1</v>
+          <t>許認可・設計・その他諸経費</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>率で入力（10%＝6,500万円）。社内のハードルレートに合わせる</t>
+          <t>工事費に含む前提で0。別建てなら入力</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>PX利益・リスク料（金額）</t>
-        </is>
-      </c>
-      <c r="C10" s="9">
-        <f>C5*C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="9">
-        <f>D5*D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="9">
-        <f>E5*E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>A×E</t>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>土地＋連系権利に払える上限（基本ケース）</t>
+        </is>
+      </c>
+      <c r="C10" s="8">
+        <f>C5-C6-C7-C8-C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="8">
+        <f>D5-D6-D7-D8-D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="8">
+        <f>E5-E6-E7-E8-E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>A−B−C−D−E</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>土地＋連系権利に払える上限（残余）</t>
-        </is>
-      </c>
-      <c r="C11" s="11">
-        <f>C5-C6-C7-C8-C10</f>
-        <v/>
-      </c>
-      <c r="D11" s="11">
-        <f>D5-D6-D7-D8-D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>E5-E6-E7-E8-E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>A−B−C−D−F。権利付き用地の市場感（約5,000万〜1.5億円）と比べる</t>
+          <t>同上（販売5.5億・機材3.3億の最良ケース）</t>
+        </is>
+      </c>
+      <c r="C11" s="8">
+        <f>55000-33000-C7-C8-C9</f>
+        <v/>
+      </c>
+      <c r="D11" s="8">
+        <f>55000-33000-D7-D8-D9</f>
+        <v/>
+      </c>
+      <c r="E11" s="8">
+        <f>55000-33000-E7-E8-E9</f>
+        <v/>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>販売上限5.5億円、機材を許容下限3.3億円まで下げた場合</t>
         </is>
       </c>
     </row>
@@ -786,18 +785,18 @@
           <t>周辺の公的地価の目安（万円/㎡）</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>白浜町住宅地の公示平均2.9万円/㎡(2026)。新庄町は田辺市平均7.0万円/㎡の非線引き郊外として控えめに仮置き。芳養は山林・畑のため低め。※地点ごとの公示地価は不動産情報ライブラリで要確認</t>
+          <t>白浜町住宅地の公示平均2.9万円/㎡(2026)。新庄町は田辺市平均7.0万円/㎡の非線引き郊外として控えめに仮置き。芳養は山林・畑のため低め。地点値は不動産情報ライブラリで要確認</t>
         </is>
       </c>
     </row>
@@ -812,15 +811,15 @@
           <t>素地の土地価値（万円）</t>
         </is>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="11">
         <f>C14*C15</f>
         <v/>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="11">
         <f>D14*D15</f>
         <v/>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="11">
         <f>E14*E15</f>
         <v/>
       </c>
@@ -838,24 +837,24 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>連系権利の価値（万円）</t>
-        </is>
-      </c>
-      <c r="C17" s="13">
-        <f>C11-C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="13">
-        <f>D11-D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>E11-E16</f>
+          <t>基本ケースで連系権利に残る価値（万円）</t>
+        </is>
+      </c>
+      <c r="C17" s="12">
+        <f>C10-C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="12">
+        <f>D10-D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>E10-E16</f>
         <v/>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>G−J。土地代を引いて権利に残る価値。マイナスなら、その土地を全部買うと採算が合わない</t>
+          <t>G−J。マイナス＝土地を全部買うと採算が合わない</t>
         </is>
       </c>
     </row>
@@ -881,7 +880,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>2MW/8MWh級は1,000〜2,000㎡で足りる例が多い（事例：952㎡）。余剰地は買わない／賃借／分筆の交渉材料</t>
+          <t>2MW/8MWh級は1,000〜2,000㎡で足りる例が多い（事例：952㎡）。余剰地は分筆・賃借の交渉材料</t>
         </is>
       </c>
     </row>
@@ -896,15 +895,15 @@
           <t>必要面積分だけ買う場合の素地価値（万円）</t>
         </is>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="11">
         <f>C18*C15</f>
         <v/>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="11">
         <f>D18*D15</f>
         <v/>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="11">
         <f>E18*E15</f>
         <v/>
       </c>
@@ -926,7 +925,7 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>【感度】土地＋権利の上限（万円）：設備費B × 完成品価値A（湯崎2の負担金・諸経費・利益率で計算）</t>
+          <t>【感度：湯崎2】土地＋権利の上限（万円）：機材B ＼ 販売価格A</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -938,73 +937,73 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>設備費B ＼ 完成品価値A</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>65000</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>70000</v>
+          <t>機材 ＼ 販売</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>52500</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>55000</v>
       </c>
       <c r="F22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="9" t="n">
-        <v>35000</v>
-      </c>
-      <c r="C23" s="9">
-        <f>C22-$B23-$C$7-$C$8-C22*$C$9</f>
-        <v/>
-      </c>
-      <c r="D23" s="9">
-        <f>D22-$B23-$C$7-$C$8-D22*$C$9</f>
-        <v/>
-      </c>
-      <c r="E23" s="9">
-        <f>E22-$B23-$C$7-$C$8-E22*$C$9</f>
+      <c r="B23" s="11" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C23" s="11">
+        <f>C22-$B23-$C$7-$C$8-$C$9</f>
+        <v/>
+      </c>
+      <c r="D23" s="11">
+        <f>D22-$B23-$C$7-$C$8-$C$9</f>
+        <v/>
+      </c>
+      <c r="E23" s="11">
+        <f>E22-$B23-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
       <c r="F23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
-      <c r="B24" s="9" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C24" s="9">
-        <f>C22-$B24-$C$7-$C$8-C22*$C$9</f>
-        <v/>
-      </c>
-      <c r="D24" s="9">
-        <f>D22-$B24-$C$7-$C$8-D22*$C$9</f>
-        <v/>
-      </c>
-      <c r="E24" s="9">
-        <f>E22-$B24-$C$7-$C$8-E22*$C$9</f>
+      <c r="B24" s="11" t="n">
+        <v>35500</v>
+      </c>
+      <c r="C24" s="11">
+        <f>C22-$B24-$C$7-$C$8-$C$9</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>D22-$B24-$C$7-$C$8-$C$9</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>E22-$B24-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
       <c r="F24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
-      <c r="B25" s="9" t="n">
-        <v>45000</v>
-      </c>
-      <c r="C25" s="9">
-        <f>C22-$B25-$C$7-$C$8-C22*$C$9</f>
-        <v/>
-      </c>
-      <c r="D25" s="9">
-        <f>D22-$B25-$C$7-$C$8-D22*$C$9</f>
-        <v/>
-      </c>
-      <c r="E25" s="9">
-        <f>E22-$B25-$C$7-$C$8-E22*$C$9</f>
+      <c r="B25" s="11" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C25" s="11">
+        <f>C22-$B25-$C$7-$C$8-$C$9</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>D22-$B25-$C$7-$C$8-$C$9</f>
+        <v/>
+      </c>
+      <c r="E25" s="11">
+        <f>E22-$B25-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n"/>
@@ -1016,6 +1015,204 @@
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>【感度：橋谷】土地＋権利の上限（万円）：機材B ＼ 販売価格A</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>機材 ＼ 販売</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>52500</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="11" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C29" s="11">
+        <f>C28-$B29-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="D29" s="11">
+        <f>D28-$B29-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="E29" s="11">
+        <f>E28-$B29-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="F29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="11" t="n">
+        <v>35500</v>
+      </c>
+      <c r="C30" s="11">
+        <f>C28-$B30-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="D30" s="11">
+        <f>D28-$B30-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="E30" s="11">
+        <f>E28-$B30-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="F30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="11" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C31" s="11">
+        <f>C28-$B31-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="D31" s="11">
+        <f>D28-$B31-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="E31" s="11">
+        <f>E28-$B31-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>【感度：芳養】土地＋権利の上限（万円）：機材B ＼ 販売価格A</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>機材 ＼ 販売</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>52500</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="11" t="n">
+        <v>38000</v>
+      </c>
+      <c r="C35" s="11">
+        <f>C34-$B35-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="D35" s="11">
+        <f>D34-$B35-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="E35" s="11">
+        <f>E34-$B35-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="F35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="11" t="n">
+        <v>35500</v>
+      </c>
+      <c r="C36" s="11">
+        <f>C34-$B36-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="D36" s="11">
+        <f>D34-$B36-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="E36" s="11">
+        <f>E34-$B36-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="F36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="11" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C37" s="11">
+        <f>C34-$B37-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="D37" s="11">
+        <f>D34-$B37-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="E37" s="11">
+        <f>E34-$B37-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="F37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1031,118 +1228,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>■ この試算の性質</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>■ 前提（PX側ヒアリング 2026-10-08）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>・PXの社内買取基準は参照していません（リポジトリ・スキルに価格基準が無いため）。公開情報と仮定で組んだ逆算モデルです。前提（黄色）を社内値に置き換えてください。</t>
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>・完成品の販売見込み：5.0〜5.5億円</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>・連系権利の譲渡可否・名義変更は関西電力送配電への確認が必要です（接続検討回答書は「連系をお約束するものではない」と明記）。</t>
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>・機材：基本3.8億円（PX見積 202511-BESS-0001 税抜3.86億円、原価2.70億円、粗利30%）。3.3億円まで許容可能</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>・回答書は再接続検討で負担金・工期が変わる可能性があると記載。負担金は確定前の概算です。</t>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>・工事費：通常約5,000万円</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr"/>
+      <c r="A5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>■ 使った公開情報</t>
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>■ 注意</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>・白浜町 住宅地 公示地価 平均 2.9万円/㎡（9.5万円/坪, 2026年）: https://totinokati.com/kakaku/place/30401/kouji/</t>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>・連系権利の名義変更可否は関西電力送配電に要確認（回答書は連系を約束するものではない）。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>・田辺市 公的地価 2026年 平均 7.04万円/㎡（市全体。新庄町・芳養の地点値ではない）: https://e-estate.jp/land/market-price/wakayama/tanabeshi/</t>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>・回答書は再接続検討で負担金・工期が変わる可能性あり。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>・権利付き用地の市場感 5,000万〜1.5億円、土地価格に権利分を数千万円上乗せ: https://tiktak-jp.com/column/apply/</t>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>・公示地価は町・市平均。地点値は不動産情報ライブラリで確認。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>・JHD（2721）荘川蓄電所 2MW/8MWh 完成品 約7億円（2026/7/30開示）: https://finance.biggo.jp/news/jpx_tdnet_140120260730503765</t>
-        </is>
-      </c>
+      <c r="A10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>・METI 系統用蓄電池コスト 6.0〜7.6万円/kWh（2022〜24年度）: https://www.meti.go.jp/shingikai/enecho/shoene_shinene/shin_energy/keito_wg/pdf/049_03_00.pdf</t>
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>■ 公開情報</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>・土地＋権利物件の例（1,957〜1,999kW・846〜3,839㎡、価格は応相談）: https://www.co-sumida.jp/chikudensho.html</t>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>・白浜町 住宅地 公示地価 平均2.9万円/㎡(2026): https://totinokati.com/kakaku/place/30401/kouji/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr"/>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>・田辺市 公的地価 2026 平均7.04万円/㎡: https://e-estate.jp/land/market-price/wakayama/tanabeshi/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>■ 案件固有の値（回答書・概要書より）</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>・権利付き用地の市場感 5,000万〜1.5億円: https://tiktak-jp.com/column/apply/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>■ 案件固有の値</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>・湯崎2: 2,528.63㎡、負担金6,370.4千円(税込)、入金後約6ヶ月</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>・橋谷: 5,699㎡、負担金12,910.9千円(税込)、入金後約12ヶ月</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>・芳養: 6,713㎡、負担金63,747.3千円(税込)、入金後約12ヶ月</t>
         </is>

--- a/docs/案件DD/土地権利買取_上限価格試算_和歌山3案件.xlsx
+++ b/docs/案件DD/土地権利買取_上限価格試算_和歌山3案件.xlsx
@@ -604,17 +604,17 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>通常約5,000万円</t>
+          <t>通常約5,000万円だが、安全側に8,000万円で計上（PX指示 2026-10-08）</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>・工事費：通常約5,000万円</t>
+          <t>・工事費：通常約5,000万円 → 安全側に8,000万円で計上</t>
         </is>
       </c>
     </row>

--- a/docs/案件DD/土地権利買取_上限価格試算_和歌山3案件.xlsx
+++ b/docs/案件DD/土地権利買取_上限価格試算_和歌山3案件.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -729,205 +729,222 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>同上（販売5.0億・機材3.3億の保守ケース）</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
+        <f>50000-33000-C7-C8-C9</f>
+        <v/>
+      </c>
+      <c r="D12" s="8">
+        <f>50000-33000-D7-D8-D9</f>
+        <v/>
+      </c>
+      <c r="E12" s="8">
+        <f>50000-33000-E7-E8-E9</f>
+        <v/>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>販売は下限5.0億円のまま、機材だけ許容下限3.3億円まで下げた場合</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>【参考】素地としての土地価値</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>公簿面積（㎡）</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>2528.63</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>5699</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>6713</v>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>物件概要書</t>
-        </is>
-      </c>
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>【参考】素地としての土地価値</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>周辺の公的地価の目安（万円/㎡）</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.8</v>
+          <t>公簿面積（㎡）</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>2528.63</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>5699</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>6713</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>白浜町住宅地の公示平均2.9万円/㎡(2026)。新庄町は田辺市平均7.0万円/㎡の非線引き郊外として控えめに仮置き。芳養は山林・畑のため低め。地点値は不動産情報ライブラリで要確認</t>
+          <t>物件概要書</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>素地の土地価値（万円）</t>
-        </is>
-      </c>
-      <c r="C16" s="11">
-        <f>C14*C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="11">
-        <f>D14*D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="11">
-        <f>E14*E15</f>
-        <v/>
+          <t>周辺の公的地価の目安（万円/㎡）</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.8</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>H×I</t>
+          <t>白浜町住宅地の公示平均2.9万円/㎡(2026)。新庄町は田辺市平均7.0万円/㎡の非線引き郊外として控えめに仮置き。芳養は山林・畑のため低め。地点値は不動産情報ライブラリで要確認</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>基本ケースで連系権利に残る価値（万円）</t>
-        </is>
-      </c>
-      <c r="C17" s="12">
-        <f>C10-C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="12">
-        <f>D10-D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="12">
-        <f>E10-E16</f>
+          <t>素地の土地価値（万円）</t>
+        </is>
+      </c>
+      <c r="C17" s="11">
+        <f>C15*C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="11">
+        <f>D15*D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="11">
+        <f>E15*E16</f>
         <v/>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>G−J。マイナス＝土地を全部買うと採算が合わない</t>
+          <t>H×I</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>BESS設置に必要な面積の目安（㎡）</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>1500</v>
+          <t>基本ケースで連系権利に残る価値（万円）</t>
+        </is>
+      </c>
+      <c r="C18" s="12">
+        <f>C10-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="12">
+        <f>D10-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>E10-E17</f>
+        <v/>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>2MW/8MWh級は1,000〜2,000㎡で足りる例が多い（事例：952㎡）。余剰地は分筆・賃借の交渉材料</t>
+          <t>G−J。マイナス＝土地を全部買うと採算が合わない</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>BESS設置に必要な面積の目安（㎡）</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>2MW/8MWh級は1,000〜2,000㎡で足りる例が多い（事例：952㎡）。余剰地は分筆・賃借の交渉材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>必要面積分だけ買う場合の素地価値（万円）</t>
         </is>
       </c>
-      <c r="C19" s="11">
-        <f>C18*C15</f>
-        <v/>
-      </c>
-      <c r="D19" s="11">
-        <f>D18*D15</f>
-        <v/>
-      </c>
-      <c r="E19" s="11">
-        <f>E18*E15</f>
-        <v/>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="C20" s="11">
+        <f>C19*C16</f>
+        <v/>
+      </c>
+      <c r="D20" s="11">
+        <f>D19*D16</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>E19*E16</f>
+        <v/>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>L×I</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>【感度：湯崎2】土地＋権利の上限（万円）：機材B ＼ 販売価格A</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
@@ -937,54 +954,47 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>機材 ＼ 販売</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>52500</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>55000</v>
-      </c>
+          <t>【感度：湯崎2】土地＋権利の上限（万円）：機材B ＼ 販売価格A</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
-      <c r="B23" s="11" t="n">
-        <v>38000</v>
-      </c>
-      <c r="C23" s="11">
-        <f>C22-$B23-$C$7-$C$8-$C$9</f>
-        <v/>
-      </c>
-      <c r="D23" s="11">
-        <f>D22-$B23-$C$7-$C$8-$C$9</f>
-        <v/>
-      </c>
-      <c r="E23" s="11">
-        <f>E22-$B23-$C$7-$C$8-$C$9</f>
-        <v/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>機材 ＼ 販売</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>52500</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>55000</v>
       </c>
       <c r="F23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="11" t="n">
-        <v>35500</v>
+        <v>38000</v>
       </c>
       <c r="C24" s="11">
-        <f>C22-$B24-$C$7-$C$8-$C$9</f>
+        <f>C23-$B24-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
       <c r="D24" s="11">
-        <f>D22-$B24-$C$7-$C$8-$C$9</f>
+        <f>D23-$B24-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
       <c r="E24" s="11">
-        <f>E22-$B24-$C$7-$C$8-$C$9</f>
+        <f>E23-$B24-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
       <c r="F24" s="5" t="n"/>
@@ -992,37 +1002,44 @@
     <row r="25">
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="11" t="n">
-        <v>33000</v>
+        <v>35500</v>
       </c>
       <c r="C25" s="11">
-        <f>C22-$B25-$C$7-$C$8-$C$9</f>
+        <f>C23-$B25-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
       <c r="D25" s="11">
-        <f>D22-$B25-$C$7-$C$8-$C$9</f>
+        <f>D23-$B25-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
       <c r="E25" s="11">
-        <f>E22-$B25-$C$7-$C$8-$C$9</f>
+        <f>E23-$B25-$C$7-$C$8-$C$9</f>
         <v/>
       </c>
       <c r="F25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
+      <c r="B26" s="11" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C26" s="11">
+        <f>C23-$B26-$C$7-$C$8-$C$9</f>
+        <v/>
+      </c>
+      <c r="D26" s="11">
+        <f>D23-$B26-$C$7-$C$8-$C$9</f>
+        <v/>
+      </c>
+      <c r="E26" s="11">
+        <f>E23-$B26-$C$7-$C$8-$C$9</f>
+        <v/>
+      </c>
       <c r="F26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>【感度：橋谷】土地＋権利の上限（万円）：機材B ＼ 販売価格A</t>
-        </is>
-      </c>
+      <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
@@ -1032,54 +1049,47 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>機材 ＼ 販売</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D28" s="13" t="n">
-        <v>52500</v>
-      </c>
-      <c r="E28" s="13" t="n">
-        <v>55000</v>
-      </c>
+          <t>【感度：橋谷】土地＋権利の上限（万円）：機材B ＼ 販売価格A</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
-      <c r="B29" s="11" t="n">
-        <v>38000</v>
-      </c>
-      <c r="C29" s="11">
-        <f>C28-$B29-$D$7-$D$8-$D$9</f>
-        <v/>
-      </c>
-      <c r="D29" s="11">
-        <f>D28-$B29-$D$7-$D$8-$D$9</f>
-        <v/>
-      </c>
-      <c r="E29" s="11">
-        <f>E28-$B29-$D$7-$D$8-$D$9</f>
-        <v/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>機材 ＼ 販売</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>52500</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>55000</v>
       </c>
       <c r="F29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="11" t="n">
-        <v>35500</v>
+        <v>38000</v>
       </c>
       <c r="C30" s="11">
-        <f>C28-$B30-$D$7-$D$8-$D$9</f>
+        <f>C29-$B30-$D$7-$D$8-$D$9</f>
         <v/>
       </c>
       <c r="D30" s="11">
-        <f>D28-$B30-$D$7-$D$8-$D$9</f>
+        <f>D29-$B30-$D$7-$D$8-$D$9</f>
         <v/>
       </c>
       <c r="E30" s="11">
-        <f>E28-$B30-$D$7-$D$8-$D$9</f>
+        <f>E29-$B30-$D$7-$D$8-$D$9</f>
         <v/>
       </c>
       <c r="F30" s="5" t="n"/>
@@ -1087,37 +1097,44 @@
     <row r="31">
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="11" t="n">
-        <v>33000</v>
+        <v>35500</v>
       </c>
       <c r="C31" s="11">
-        <f>C28-$B31-$D$7-$D$8-$D$9</f>
+        <f>C29-$B31-$D$7-$D$8-$D$9</f>
         <v/>
       </c>
       <c r="D31" s="11">
-        <f>D28-$B31-$D$7-$D$8-$D$9</f>
+        <f>D29-$B31-$D$7-$D$8-$D$9</f>
         <v/>
       </c>
       <c r="E31" s="11">
-        <f>E28-$B31-$D$7-$D$8-$D$9</f>
+        <f>E29-$B31-$D$7-$D$8-$D$9</f>
         <v/>
       </c>
       <c r="F31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
+      <c r="B32" s="11" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C32" s="11">
+        <f>C29-$B32-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="D32" s="11">
+        <f>D29-$B32-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
+      <c r="E32" s="11">
+        <f>E29-$B32-$D$7-$D$8-$D$9</f>
+        <v/>
+      </c>
       <c r="F32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>【感度：芳養】土地＋権利の上限（万円）：機材B ＼ 販売価格A</t>
-        </is>
-      </c>
+      <c r="B33" s="5" t="n"/>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
@@ -1127,54 +1144,47 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>機材 ＼ 販売</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D34" s="13" t="n">
-        <v>52500</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>55000</v>
-      </c>
+          <t>【感度：芳養】土地＋権利の上限（万円）：機材B ＼ 販売価格A</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
-      <c r="B35" s="11" t="n">
-        <v>38000</v>
-      </c>
-      <c r="C35" s="11">
-        <f>C34-$B35-$E$7-$E$8-$E$9</f>
-        <v/>
-      </c>
-      <c r="D35" s="11">
-        <f>D34-$B35-$E$7-$E$8-$E$9</f>
-        <v/>
-      </c>
-      <c r="E35" s="11">
-        <f>E34-$B35-$E$7-$E$8-$E$9</f>
-        <v/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>機材 ＼ 販売</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>52500</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>55000</v>
       </c>
       <c r="F35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="11" t="n">
-        <v>35500</v>
+        <v>38000</v>
       </c>
       <c r="C36" s="11">
-        <f>C34-$B36-$E$7-$E$8-$E$9</f>
+        <f>C35-$B36-$E$7-$E$8-$E$9</f>
         <v/>
       </c>
       <c r="D36" s="11">
-        <f>D34-$B36-$E$7-$E$8-$E$9</f>
+        <f>D35-$B36-$E$7-$E$8-$E$9</f>
         <v/>
       </c>
       <c r="E36" s="11">
-        <f>E34-$B36-$E$7-$E$8-$E$9</f>
+        <f>E35-$B36-$E$7-$E$8-$E$9</f>
         <v/>
       </c>
       <c r="F36" s="5" t="n"/>
@@ -1182,28 +1192,39 @@
     <row r="37">
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="11" t="n">
-        <v>33000</v>
+        <v>35500</v>
       </c>
       <c r="C37" s="11">
-        <f>C34-$B37-$E$7-$E$8-$E$9</f>
+        <f>C35-$B37-$E$7-$E$8-$E$9</f>
         <v/>
       </c>
       <c r="D37" s="11">
-        <f>D34-$B37-$E$7-$E$8-$E$9</f>
+        <f>D35-$B37-$E$7-$E$8-$E$9</f>
         <v/>
       </c>
       <c r="E37" s="11">
-        <f>E34-$B37-$E$7-$E$8-$E$9</f>
+        <f>E35-$B37-$E$7-$E$8-$E$9</f>
         <v/>
       </c>
       <c r="F37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
+      <c r="B38" s="11" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C38" s="11">
+        <f>C35-$B38-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="D38" s="11">
+        <f>D35-$B38-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
+      <c r="E38" s="11">
+        <f>E35-$B38-$E$7-$E$8-$E$9</f>
+        <v/>
+      </c>
       <c r="F38" s="5" t="n"/>
     </row>
     <row r="39">
@@ -1213,6 +1234,14 @@
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/案件DD/土地権利買取_上限価格試算_和歌山3案件.xlsx
+++ b/docs/案件DD/土地権利買取_上限価格試算_和歌山3案件.xlsx
@@ -811,21 +811,21 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>周辺の公的地価の目安（万円/㎡）</t>
+          <t>素地の実勢単価の目安（万円/㎡）</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>白浜町住宅地の公示平均2.9万円/㎡(2026)。新庄町は田辺市平均7.0万円/㎡の非線引き郊外として控えめに仮置き。芳養は山林・畑のため低め。地点値は不動産情報ライブラリで要確認</t>
+          <t>実勢ベース。湯崎2: 用途地域は住居系だが雑木・未造成の大面積→白浜町の取引相場（全地目で取引額中央値300〜420万円）から1.0。橋谷: 更地だが非線引き・工業地隣接の大面積→新庄町の宅地事例2万円/㎡の半分で1.0。芳養: 山林・畑→0.3。公示住宅地（白浜2.9・田辺7.0）は小区画宅地の値で、ここには当てはまらない</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1335,50 +1335,64 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>・白浜町 住宅地 公示地価 平均2.9万円/㎡(2026): https://totinokati.com/kakaku/place/30401/kouji/</t>
+          <t>・白浜町 住宅地 公示地価 平均2.9万円/㎡(2026)※小区画宅地の参考: https://totinokati.com/kakaku/place/30401/kouji/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>・田辺市 公的地価 2026 平均7.04万円/㎡: https://e-estate.jp/land/market-price/wakayama/tanabeshi/</t>
+          <t>・白浜町 取引相場（全地目）2022〜24年 取引額300〜420万円/件: https://e-estate.jp/land/market-price/wakayama/nishimurogunshirahamachou/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>・権利付き用地の市場感 5,000万〜1.5億円: https://tiktak-jp.com/column/apply/</t>
+          <t>・田辺市 売却事例 新庄町 2万円/㎡(2025)・芳養町 3万円/㎡(2022)・中芳養 2万円/㎡(2025)、いずれも30坪台の宅地: https://e-estate.jp/land/market-price/wakayama/tanabeshi/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr"/>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>・田辺市 公的地価 2026 平均7.04万円/㎡: https://e-estate.jp/land/market-price/wakayama/tanabeshi/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>■ 案件固有の値</t>
+          <t>・権利付き用地の市場感 5,000万〜1.5億円: https://tiktak-jp.com/column/apply/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>・湯崎2: 2,528.63㎡、負担金6,370.4千円(税込)、入金後約6ヶ月</t>
-        </is>
-      </c>
+      <c r="A17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>・橋谷: 5,699㎡、負担金12,910.9千円(税込)、入金後約12ヶ月</t>
+          <t>■ 案件固有の値</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>・湯崎2: 2,528.63㎡、負担金6,370.4千円(税込)、入金後約6ヶ月</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>・橋谷: 5,699㎡、負担金12,910.9千円(税込)、入金後約12ヶ月</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>・芳養: 6,713㎡、負担金63,747.3千円(税込)、入金後約12ヶ月</t>
         </is>
